--- a/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>SSUMY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,43 +656,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -702,23 +702,26 @@
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>45952500</v>
+        <v>44087700</v>
       </c>
       <c r="E8" s="3">
-        <v>37036400</v>
+        <v>43498000</v>
       </c>
       <c r="F8" s="3">
-        <v>31307700</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
+        <v>35058200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>29635500</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -729,23 +732,26 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>37630200</v>
+        <v>35522700</v>
       </c>
       <c r="E9" s="3">
-        <v>30231700</v>
+        <v>35620300</v>
       </c>
       <c r="F9" s="3">
-        <v>26391100</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+        <v>28616900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>24981500</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -756,23 +762,26 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8322200</v>
+        <v>8565100</v>
       </c>
       <c r="E10" s="3">
-        <v>6804700</v>
+        <v>7877700</v>
       </c>
       <c r="F10" s="3">
-        <v>4916600</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+        <v>6441300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4654000</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -783,9 +792,12 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,8 +809,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -823,9 +836,12 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,23 +866,26 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>46200</v>
+        <v>238700</v>
       </c>
       <c r="E14" s="3">
-        <v>120600</v>
+        <v>43800</v>
       </c>
       <c r="F14" s="3">
-        <v>545700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>114100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>516600</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -877,23 +896,26 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>119300</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>116500</v>
+        <v>112900</v>
       </c>
       <c r="F15" s="3">
-        <v>130500</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+        <v>110300</v>
+      </c>
+      <c r="G15" s="3">
+        <v>123500</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -904,9 +926,12 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,22 +940,23 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>43033600</v>
+        <v>41827900</v>
       </c>
       <c r="E17" s="3">
-        <v>34752200</v>
+        <v>40735100</v>
       </c>
       <c r="F17" s="3">
-        <v>31704600</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
+        <v>32896000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>30011100</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -941,23 +967,26 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2918900</v>
+        <v>2259800</v>
       </c>
       <c r="E18" s="3">
-        <v>2284200</v>
+        <v>2763000</v>
       </c>
       <c r="F18" s="3">
-        <v>-396900</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
+        <v>2162200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-375700</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -968,9 +997,12 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,22 +1014,23 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2356600</v>
+        <v>1670100</v>
       </c>
       <c r="E20" s="3">
-        <v>1896000</v>
+        <v>2613500</v>
       </c>
       <c r="F20" s="3">
-        <v>-31400</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+        <v>1794800</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-29700</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1008,23 +1041,26 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6519400</v>
+        <v>5205000</v>
       </c>
       <c r="E21" s="3">
-        <v>5333600</v>
+        <v>6546900</v>
       </c>
       <c r="F21" s="3">
-        <v>728800</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+        <v>5042200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>683300</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1035,23 +1071,26 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>403000</v>
+        <v>563500</v>
       </c>
       <c r="E22" s="3">
-        <v>203500</v>
+        <v>762900</v>
       </c>
       <c r="F22" s="3">
-        <v>206800</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+        <v>192600</v>
+      </c>
+      <c r="G22" s="3">
+        <v>195700</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1062,23 +1101,26 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4872500</v>
+        <v>3366400</v>
       </c>
       <c r="E23" s="3">
-        <v>3976700</v>
+        <v>4613500</v>
       </c>
       <c r="F23" s="3">
-        <v>-635000</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
+        <v>3764300</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-601100</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1089,23 +1131,26 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>834600</v>
+        <v>647800</v>
       </c>
       <c r="E24" s="3">
-        <v>710700</v>
+        <v>790300</v>
       </c>
       <c r="F24" s="3">
-        <v>271400</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+        <v>672800</v>
+      </c>
+      <c r="G24" s="3">
+        <v>256900</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1116,9 +1161,12 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,23 +1191,26 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4037900</v>
+        <v>2718600</v>
       </c>
       <c r="E26" s="3">
-        <v>3266000</v>
+        <v>3823200</v>
       </c>
       <c r="F26" s="3">
-        <v>-906400</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
+        <v>3091500</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-858000</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1170,23 +1221,26 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3807600</v>
+        <v>2463600</v>
       </c>
       <c r="E27" s="3">
-        <v>3123900</v>
+        <v>3605200</v>
       </c>
       <c r="F27" s="3">
-        <v>-1031300</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
+        <v>2957000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-976200</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1197,9 +1251,12 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,9 +1281,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,9 +1311,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,23 +1371,26 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2356600</v>
+        <v>-1670100</v>
       </c>
       <c r="E32" s="3">
-        <v>-1896000</v>
+        <v>-2613500</v>
       </c>
       <c r="F32" s="3">
-        <v>31400</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+        <v>-1794800</v>
+      </c>
+      <c r="G32" s="3">
+        <v>29700</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1332,23 +1401,26 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3807600</v>
+        <v>2463600</v>
       </c>
       <c r="E33" s="3">
-        <v>3123900</v>
+        <v>3605200</v>
       </c>
       <c r="F33" s="3">
-        <v>-1031300</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
+        <v>2957000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-976200</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1359,9 +1431,12 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,23 +1461,26 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3807600</v>
+        <v>2463600</v>
       </c>
       <c r="E35" s="3">
-        <v>3123900</v>
+        <v>3605200</v>
       </c>
       <c r="F35" s="3">
-        <v>-1031300</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
+        <v>2957000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-976200</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1413,29 +1491,32 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1445,9 +1526,12 @@
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,22 +1557,23 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4499900</v>
+        <v>4327500</v>
       </c>
       <c r="E41" s="3">
-        <v>5039300</v>
+        <v>4259600</v>
       </c>
       <c r="F41" s="3">
-        <v>4123300</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+        <v>4770100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3903100</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1498,23 +1584,26 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>846300</v>
+        <v>1211100</v>
       </c>
       <c r="E42" s="3">
-        <v>1706600</v>
+        <v>801100</v>
       </c>
       <c r="F42" s="3">
-        <v>786300</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+        <v>1615400</v>
+      </c>
+      <c r="G42" s="3">
+        <v>744300</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1525,23 +1614,26 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14190200</v>
+        <v>14576500</v>
       </c>
       <c r="E43" s="3">
-        <v>12957000</v>
+        <v>13432200</v>
       </c>
       <c r="F43" s="3">
-        <v>10059000</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+        <v>12264900</v>
+      </c>
+      <c r="G43" s="3">
+        <v>9521700</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1552,23 +1644,26 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>18744700</v>
+        <v>9485600</v>
       </c>
       <c r="E44" s="3">
-        <v>7130900</v>
+        <v>17743500</v>
       </c>
       <c r="F44" s="3">
-        <v>5346700</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+        <v>6750100</v>
+      </c>
+      <c r="G44" s="3">
+        <v>5061100</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1579,23 +1674,26 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3935000</v>
+        <v>3803000</v>
       </c>
       <c r="E45" s="3">
-        <v>4476800</v>
+        <v>3724800</v>
       </c>
       <c r="F45" s="3">
-        <v>3258400</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+        <v>4237600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3084400</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1606,23 +1704,26 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>32843700</v>
+        <v>33403800</v>
       </c>
       <c r="E46" s="3">
-        <v>31310600</v>
+        <v>31089500</v>
       </c>
       <c r="F46" s="3">
-        <v>23573700</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+        <v>29638200</v>
+      </c>
+      <c r="G46" s="3">
+        <v>22314600</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1633,23 +1734,26 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>20487300</v>
+        <v>24072800</v>
       </c>
       <c r="E47" s="3">
-        <v>18719300</v>
+        <v>21873300</v>
       </c>
       <c r="F47" s="3">
-        <v>16370800</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+        <v>20377800</v>
+      </c>
+      <c r="G47" s="3">
+        <v>18156500</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1660,23 +1764,26 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>18773200</v>
+        <v>9910900</v>
       </c>
       <c r="E48" s="3">
-        <v>9187100</v>
+        <v>18005800</v>
       </c>
       <c r="F48" s="3">
-        <v>9376000</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+        <v>8953100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>9042300</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1687,23 +1794,26 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3839000</v>
+        <v>2231900</v>
       </c>
       <c r="E49" s="3">
-        <v>1718500</v>
+        <v>3633900</v>
       </c>
       <c r="F49" s="3">
-        <v>1725200</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
+        <v>1626700</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1633000</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1714,9 +1824,12 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,23 +1884,26 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3473200</v>
+        <v>768500</v>
       </c>
       <c r="E52" s="3">
-        <v>3648400</v>
+        <v>572000</v>
       </c>
       <c r="F52" s="3">
-        <v>3413300</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+        <v>538500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>403900</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1795,9 +1914,12 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,23 +1944,26 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>68110300</v>
+        <v>70387900</v>
       </c>
       <c r="E54" s="3">
-        <v>64583800</v>
+        <v>64472300</v>
       </c>
       <c r="F54" s="3">
-        <v>54459100</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+        <v>61134200</v>
+      </c>
+      <c r="G54" s="3">
+        <v>51550300</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1849,9 +1974,12 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,22 +2005,23 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11114100</v>
+        <v>10934900</v>
       </c>
       <c r="E57" s="3">
-        <v>10868100</v>
+        <v>10520500</v>
       </c>
       <c r="F57" s="3">
-        <v>8557300</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+        <v>10287600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>8100200</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1902,23 +2032,26 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9751200</v>
+        <v>5249700</v>
       </c>
       <c r="E58" s="3">
-        <v>4595700</v>
+        <v>9230400</v>
       </c>
       <c r="F58" s="3">
-        <v>3700700</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>4350200</v>
+      </c>
+      <c r="G58" s="3">
+        <v>3503100</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -1929,23 +2062,26 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3739100</v>
+        <v>3852300</v>
       </c>
       <c r="E59" s="3">
-        <v>5273800</v>
+        <v>3539400</v>
       </c>
       <c r="F59" s="3">
-        <v>3031000</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+        <v>4992100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2869100</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1956,23 +2092,26 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>19985100</v>
+        <v>20036900</v>
       </c>
       <c r="E60" s="3">
-        <v>20737600</v>
+        <v>18917700</v>
       </c>
       <c r="F60" s="3">
-        <v>15289100</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
+        <v>19629900</v>
+      </c>
+      <c r="G60" s="3">
+        <v>14472400</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1983,23 +2122,26 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19468400</v>
+        <v>18399900</v>
       </c>
       <c r="E61" s="3">
-        <v>19029500</v>
+        <v>18428600</v>
       </c>
       <c r="F61" s="3">
-        <v>19307000</v>
+        <v>18013100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>18275800</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2010,23 +2152,26 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1854500</v>
+        <v>2141700</v>
       </c>
       <c r="E62" s="3">
-        <v>2026900</v>
+        <v>1755400</v>
       </c>
       <c r="F62" s="3">
-        <v>1695000</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+        <v>1918600</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1604500</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2037,9 +2182,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,23 +2272,26 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>42641900</v>
+        <v>42025600</v>
       </c>
       <c r="E66" s="3">
-        <v>43030500</v>
+        <v>40364300</v>
       </c>
       <c r="F66" s="3">
-        <v>37420700</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
+        <v>40732200</v>
+      </c>
+      <c r="G66" s="3">
+        <v>35422000</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2145,9 +2302,12 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,23 +2436,26 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18242200</v>
+        <v>18489600</v>
       </c>
       <c r="E72" s="3">
-        <v>15297500</v>
+        <v>17267800</v>
       </c>
       <c r="F72" s="3">
-        <v>12613300</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+        <v>14480400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>11939600</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2293,9 +2466,12 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,23 +2556,26 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>25468400</v>
+        <v>28362300</v>
       </c>
       <c r="E76" s="3">
-        <v>21553300</v>
+        <v>24108100</v>
       </c>
       <c r="F76" s="3">
-        <v>17038400</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
+        <v>20402100</v>
+      </c>
+      <c r="G76" s="3">
+        <v>16128300</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2401,9 +2586,12 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,29 +2616,32 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2460,23 +2651,26 @@
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3807600</v>
+        <v>2463600</v>
       </c>
       <c r="E81" s="3">
-        <v>3123900</v>
+        <v>3605200</v>
       </c>
       <c r="F81" s="3">
-        <v>-1031300</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
+        <v>2957000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-976200</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2487,9 +2681,12 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,22 +2698,23 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1238500</v>
+        <v>1277100</v>
       </c>
       <c r="E83" s="3">
-        <v>1148200</v>
+        <v>1172300</v>
       </c>
       <c r="F83" s="3">
-        <v>1151900</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+        <v>1086900</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1090400</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2527,9 +2725,12 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,23 +2875,26 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1604500</v>
+        <v>3909400</v>
       </c>
       <c r="E89" s="3">
-        <v>1247100</v>
+        <v>1518800</v>
       </c>
       <c r="F89" s="3">
-        <v>3147400</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>1180500</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2979200</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2689,9 +2905,12 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,22 +2922,23 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-473800</v>
+        <v>-595800</v>
       </c>
       <c r="E91" s="3">
-        <v>-469900</v>
+        <v>-448500</v>
       </c>
       <c r="F91" s="3">
-        <v>-447100</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+        <v>-444800</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-423300</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -2729,9 +2949,12 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,23 +3009,26 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-616900</v>
+        <v>-1398600</v>
       </c>
       <c r="E94" s="3">
-        <v>330500</v>
+        <v>-583900</v>
       </c>
       <c r="F94" s="3">
-        <v>-809500</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>312900</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-766300</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -2810,9 +3039,12 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,22 +3056,23 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1032200</v>
+        <v>-939900</v>
       </c>
       <c r="E96" s="3">
-        <v>-673900</v>
+        <v>-977000</v>
       </c>
       <c r="F96" s="3">
-        <v>-589500</v>
+        <v>-637900</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-558000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -2850,9 +3083,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,23 +3173,26 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1688100</v>
+        <v>-2650700</v>
       </c>
       <c r="E100" s="3">
-        <v>-943100</v>
+        <v>-1597900</v>
       </c>
       <c r="F100" s="3">
-        <v>-3143300</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+        <v>-892700</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-2975400</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -2958,23 +3203,26 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>181700</v>
+        <v>210000</v>
       </c>
       <c r="E101" s="3">
-        <v>274100</v>
+        <v>172000</v>
       </c>
       <c r="F101" s="3">
-        <v>54900</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+        <v>259500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>52000</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -2985,23 +3233,26 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-518700</v>
+        <v>70100</v>
       </c>
       <c r="E102" s="3">
-        <v>908600</v>
+        <v>-491000</v>
       </c>
       <c r="F102" s="3">
-        <v>-750600</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+        <v>860100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-710500</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3012,7 +3263,10 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>SSUMY</t>
   </si>
@@ -712,16 +712,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>44087700</v>
+        <v>49063100</v>
       </c>
       <c r="E8" s="3">
-        <v>43498000</v>
+        <v>48406900</v>
       </c>
       <c r="F8" s="3">
-        <v>35058200</v>
+        <v>39014600</v>
       </c>
       <c r="G8" s="3">
-        <v>29635500</v>
+        <v>32979900</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -742,16 +742,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>35522700</v>
+        <v>39531500</v>
       </c>
       <c r="E9" s="3">
-        <v>35620300</v>
+        <v>39640200</v>
       </c>
       <c r="F9" s="3">
-        <v>28616900</v>
+        <v>31846400</v>
       </c>
       <c r="G9" s="3">
-        <v>24981500</v>
+        <v>27800700</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -772,16 +772,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8565100</v>
+        <v>9531700</v>
       </c>
       <c r="E10" s="3">
-        <v>7877700</v>
+        <v>8766700</v>
       </c>
       <c r="F10" s="3">
-        <v>6441300</v>
+        <v>7168200</v>
       </c>
       <c r="G10" s="3">
-        <v>4654000</v>
+        <v>5179200</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -876,16 +876,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>238700</v>
+        <v>265600</v>
       </c>
       <c r="E14" s="3">
-        <v>43800</v>
+        <v>48700</v>
       </c>
       <c r="F14" s="3">
-        <v>114100</v>
+        <v>127000</v>
       </c>
       <c r="G14" s="3">
-        <v>516600</v>
+        <v>574900</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -905,17 +905,17 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>156600</v>
       </c>
       <c r="E15" s="3">
-        <v>112900</v>
+        <v>125700</v>
       </c>
       <c r="F15" s="3">
-        <v>110300</v>
+        <v>122700</v>
       </c>
       <c r="G15" s="3">
-        <v>123500</v>
+        <v>137400</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -947,16 +947,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>41827900</v>
+        <v>46548300</v>
       </c>
       <c r="E17" s="3">
-        <v>40735100</v>
+        <v>45332100</v>
       </c>
       <c r="F17" s="3">
-        <v>32896000</v>
+        <v>36608400</v>
       </c>
       <c r="G17" s="3">
-        <v>30011100</v>
+        <v>33398000</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -977,16 +977,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2259800</v>
+        <v>2514800</v>
       </c>
       <c r="E18" s="3">
-        <v>2763000</v>
+        <v>3074800</v>
       </c>
       <c r="F18" s="3">
-        <v>2162200</v>
+        <v>2406200</v>
       </c>
       <c r="G18" s="3">
-        <v>-375700</v>
+        <v>-418100</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1021,16 +1021,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1670100</v>
+        <v>1858600</v>
       </c>
       <c r="E20" s="3">
-        <v>2613500</v>
+        <v>2483900</v>
       </c>
       <c r="F20" s="3">
-        <v>1794800</v>
+        <v>1997300</v>
       </c>
       <c r="G20" s="3">
-        <v>-29700</v>
+        <v>-33000</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1051,16 +1051,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5205000</v>
+        <v>5784600</v>
       </c>
       <c r="E21" s="3">
-        <v>6546900</v>
+        <v>6854100</v>
       </c>
       <c r="F21" s="3">
-        <v>5042200</v>
+        <v>5604600</v>
       </c>
       <c r="G21" s="3">
-        <v>683300</v>
+        <v>753800</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1081,16 +1081,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>563500</v>
+        <v>627100</v>
       </c>
       <c r="E22" s="3">
-        <v>762900</v>
+        <v>424500</v>
       </c>
       <c r="F22" s="3">
-        <v>192600</v>
+        <v>214400</v>
       </c>
       <c r="G22" s="3">
-        <v>195700</v>
+        <v>217800</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1111,16 +1111,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3366400</v>
+        <v>3746300</v>
       </c>
       <c r="E23" s="3">
-        <v>4613500</v>
+        <v>5134200</v>
       </c>
       <c r="F23" s="3">
-        <v>3764300</v>
+        <v>4189100</v>
       </c>
       <c r="G23" s="3">
-        <v>-601100</v>
+        <v>-668900</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1141,16 +1141,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>647800</v>
+        <v>720900</v>
       </c>
       <c r="E24" s="3">
-        <v>790300</v>
+        <v>879500</v>
       </c>
       <c r="F24" s="3">
-        <v>672800</v>
+        <v>748700</v>
       </c>
       <c r="G24" s="3">
-        <v>256900</v>
+        <v>285900</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1201,16 +1201,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2718600</v>
+        <v>3025400</v>
       </c>
       <c r="E26" s="3">
-        <v>3823200</v>
+        <v>4254700</v>
       </c>
       <c r="F26" s="3">
-        <v>3091500</v>
+        <v>3440400</v>
       </c>
       <c r="G26" s="3">
-        <v>-858000</v>
+        <v>-954800</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2463600</v>
+        <v>2741600</v>
       </c>
       <c r="E27" s="3">
-        <v>3605200</v>
+        <v>4012000</v>
       </c>
       <c r="F27" s="3">
-        <v>2957000</v>
+        <v>3290700</v>
       </c>
       <c r="G27" s="3">
-        <v>-976200</v>
+        <v>-1086400</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1381,16 +1381,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1670100</v>
+        <v>-1858600</v>
       </c>
       <c r="E32" s="3">
-        <v>-2613500</v>
+        <v>-2483900</v>
       </c>
       <c r="F32" s="3">
-        <v>-1794800</v>
+        <v>-1997300</v>
       </c>
       <c r="G32" s="3">
-        <v>29700</v>
+        <v>33000</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1411,16 +1411,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2463600</v>
+        <v>2741600</v>
       </c>
       <c r="E33" s="3">
-        <v>3605200</v>
+        <v>4012000</v>
       </c>
       <c r="F33" s="3">
-        <v>2957000</v>
+        <v>3290700</v>
       </c>
       <c r="G33" s="3">
-        <v>-976200</v>
+        <v>-1086400</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1471,16 +1471,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2463600</v>
+        <v>2741600</v>
       </c>
       <c r="E35" s="3">
-        <v>3605200</v>
+        <v>4012000</v>
       </c>
       <c r="F35" s="3">
-        <v>2957000</v>
+        <v>3290700</v>
       </c>
       <c r="G35" s="3">
-        <v>-976200</v>
+        <v>-1086400</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1564,16 +1564,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4327500</v>
+        <v>4815900</v>
       </c>
       <c r="E41" s="3">
-        <v>4259600</v>
+        <v>4740300</v>
       </c>
       <c r="F41" s="3">
-        <v>4770100</v>
+        <v>5308500</v>
       </c>
       <c r="G41" s="3">
-        <v>3903100</v>
+        <v>4343500</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1594,16 +1594,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1211100</v>
+        <v>1347800</v>
       </c>
       <c r="E42" s="3">
-        <v>801100</v>
+        <v>891500</v>
       </c>
       <c r="F42" s="3">
-        <v>1615400</v>
+        <v>1797700</v>
       </c>
       <c r="G42" s="3">
-        <v>744300</v>
+        <v>828300</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1624,16 +1624,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14576500</v>
+        <v>16221500</v>
       </c>
       <c r="E43" s="3">
-        <v>13432200</v>
+        <v>14948100</v>
       </c>
       <c r="F43" s="3">
-        <v>12264900</v>
+        <v>13649000</v>
       </c>
       <c r="G43" s="3">
-        <v>9521700</v>
+        <v>10596300</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1654,16 +1654,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9485600</v>
+        <v>10556100</v>
       </c>
       <c r="E44" s="3">
-        <v>17743500</v>
+        <v>19745900</v>
       </c>
       <c r="F44" s="3">
-        <v>6750100</v>
+        <v>7511800</v>
       </c>
       <c r="G44" s="3">
-        <v>5061100</v>
+        <v>5632300</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1684,16 +1684,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3803000</v>
+        <v>4232200</v>
       </c>
       <c r="E45" s="3">
-        <v>3724800</v>
+        <v>4145200</v>
       </c>
       <c r="F45" s="3">
-        <v>4237600</v>
+        <v>4715900</v>
       </c>
       <c r="G45" s="3">
-        <v>3084400</v>
+        <v>3432500</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1714,16 +1714,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>33403800</v>
+        <v>37173500</v>
       </c>
       <c r="E46" s="3">
-        <v>31089500</v>
+        <v>34598000</v>
       </c>
       <c r="F46" s="3">
-        <v>29638200</v>
+        <v>32982900</v>
       </c>
       <c r="G46" s="3">
-        <v>22314600</v>
+        <v>24832800</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1744,16 +1744,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>24072800</v>
+        <v>26789500</v>
       </c>
       <c r="E47" s="3">
-        <v>21873300</v>
+        <v>24341800</v>
       </c>
       <c r="F47" s="3">
-        <v>20377800</v>
+        <v>22677400</v>
       </c>
       <c r="G47" s="3">
-        <v>18156500</v>
+        <v>20205500</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1774,16 +1774,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9910900</v>
+        <v>11269100</v>
       </c>
       <c r="E48" s="3">
-        <v>18005800</v>
+        <v>20037900</v>
       </c>
       <c r="F48" s="3">
-        <v>8953100</v>
+        <v>9963500</v>
       </c>
       <c r="G48" s="3">
-        <v>9042300</v>
+        <v>10062700</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1804,16 +1804,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2231900</v>
+        <v>2483800</v>
       </c>
       <c r="E49" s="3">
-        <v>3633900</v>
+        <v>4044000</v>
       </c>
       <c r="F49" s="3">
-        <v>1626700</v>
+        <v>1810300</v>
       </c>
       <c r="G49" s="3">
-        <v>1633000</v>
+        <v>1817300</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1894,16 +1894,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>768500</v>
+        <v>615500</v>
       </c>
       <c r="E52" s="3">
-        <v>572000</v>
+        <v>636500</v>
       </c>
       <c r="F52" s="3">
-        <v>538500</v>
+        <v>599200</v>
       </c>
       <c r="G52" s="3">
-        <v>403900</v>
+        <v>449500</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1954,16 +1954,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>70387900</v>
+        <v>78331300</v>
       </c>
       <c r="E54" s="3">
-        <v>64472300</v>
+        <v>71748200</v>
       </c>
       <c r="F54" s="3">
-        <v>61134200</v>
+        <v>68033400</v>
       </c>
       <c r="G54" s="3">
-        <v>51550300</v>
+        <v>57367900</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2012,16 +2012,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10934900</v>
+        <v>12168900</v>
       </c>
       <c r="E57" s="3">
-        <v>10520500</v>
+        <v>11707700</v>
       </c>
       <c r="F57" s="3">
-        <v>10287600</v>
+        <v>11448600</v>
       </c>
       <c r="G57" s="3">
-        <v>8100200</v>
+        <v>9014400</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2042,16 +2042,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5249700</v>
+        <v>5842100</v>
       </c>
       <c r="E58" s="3">
-        <v>9230400</v>
+        <v>10272100</v>
       </c>
       <c r="F58" s="3">
-        <v>4350200</v>
+        <v>4841100</v>
       </c>
       <c r="G58" s="3">
-        <v>3503100</v>
+        <v>3898400</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2072,16 +2072,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3852300</v>
+        <v>4287100</v>
       </c>
       <c r="E59" s="3">
-        <v>3539400</v>
+        <v>3938800</v>
       </c>
       <c r="F59" s="3">
-        <v>4992100</v>
+        <v>5555500</v>
       </c>
       <c r="G59" s="3">
-        <v>2869100</v>
+        <v>3192900</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2102,16 +2102,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>20036900</v>
+        <v>22298100</v>
       </c>
       <c r="E60" s="3">
-        <v>18917700</v>
+        <v>21052600</v>
       </c>
       <c r="F60" s="3">
-        <v>19629900</v>
+        <v>21845200</v>
       </c>
       <c r="G60" s="3">
-        <v>14472400</v>
+        <v>16105700</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2132,16 +2132,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18399900</v>
+        <v>20476400</v>
       </c>
       <c r="E61" s="3">
-        <v>18428600</v>
+        <v>20508300</v>
       </c>
       <c r="F61" s="3">
-        <v>18013100</v>
+        <v>20045900</v>
       </c>
       <c r="G61" s="3">
-        <v>18275800</v>
+        <v>20338200</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2162,16 +2162,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2141700</v>
+        <v>2383400</v>
       </c>
       <c r="E62" s="3">
-        <v>1755400</v>
+        <v>1953500</v>
       </c>
       <c r="F62" s="3">
-        <v>1918600</v>
+        <v>2135100</v>
       </c>
       <c r="G62" s="3">
-        <v>1604500</v>
+        <v>1785500</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2282,16 +2282,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>42025600</v>
+        <v>46768300</v>
       </c>
       <c r="E66" s="3">
-        <v>40364300</v>
+        <v>44919500</v>
       </c>
       <c r="F66" s="3">
-        <v>40732200</v>
+        <v>45328900</v>
       </c>
       <c r="G66" s="3">
-        <v>35422000</v>
+        <v>39419400</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2446,16 +2446,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18489600</v>
+        <v>20576200</v>
       </c>
       <c r="E72" s="3">
-        <v>17267800</v>
+        <v>19216600</v>
       </c>
       <c r="F72" s="3">
-        <v>14480400</v>
+        <v>16114600</v>
       </c>
       <c r="G72" s="3">
-        <v>11939600</v>
+        <v>13287000</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2566,16 +2566,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>28362300</v>
+        <v>31563000</v>
       </c>
       <c r="E76" s="3">
-        <v>24108100</v>
+        <v>26828700</v>
       </c>
       <c r="F76" s="3">
-        <v>20402100</v>
+        <v>22704500</v>
       </c>
       <c r="G76" s="3">
-        <v>16128300</v>
+        <v>17948500</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2661,16 +2661,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2463600</v>
+        <v>2741600</v>
       </c>
       <c r="E81" s="3">
-        <v>3605200</v>
+        <v>4012000</v>
       </c>
       <c r="F81" s="3">
-        <v>2957000</v>
+        <v>3290700</v>
       </c>
       <c r="G81" s="3">
-        <v>-976200</v>
+        <v>-1086400</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2705,16 +2705,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1277100</v>
+        <v>1421200</v>
       </c>
       <c r="E83" s="3">
-        <v>1172300</v>
+        <v>1304600</v>
       </c>
       <c r="F83" s="3">
-        <v>1086900</v>
+        <v>1209600</v>
       </c>
       <c r="G83" s="3">
-        <v>1090400</v>
+        <v>1213400</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2885,16 +2885,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3909400</v>
+        <v>4350600</v>
       </c>
       <c r="E89" s="3">
-        <v>1518800</v>
+        <v>1690200</v>
       </c>
       <c r="F89" s="3">
-        <v>1180500</v>
+        <v>1313700</v>
       </c>
       <c r="G89" s="3">
-        <v>2979200</v>
+        <v>3315500</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2929,16 +2929,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-595800</v>
+        <v>-663000</v>
       </c>
       <c r="E91" s="3">
-        <v>-448500</v>
+        <v>-499100</v>
       </c>
       <c r="F91" s="3">
-        <v>-444800</v>
+        <v>-495000</v>
       </c>
       <c r="G91" s="3">
-        <v>-423300</v>
+        <v>-471000</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3019,16 +3019,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1398600</v>
+        <v>-1556400</v>
       </c>
       <c r="E94" s="3">
-        <v>-583900</v>
+        <v>-649800</v>
       </c>
       <c r="F94" s="3">
-        <v>312900</v>
+        <v>348200</v>
       </c>
       <c r="G94" s="3">
-        <v>-766300</v>
+        <v>-852800</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3063,16 +3063,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-939900</v>
+        <v>-1046000</v>
       </c>
       <c r="E96" s="3">
-        <v>-977000</v>
+        <v>-1087300</v>
       </c>
       <c r="F96" s="3">
-        <v>-637900</v>
+        <v>-709900</v>
       </c>
       <c r="G96" s="3">
-        <v>-558000</v>
+        <v>-621000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -3183,16 +3183,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2650700</v>
+        <v>-2949900</v>
       </c>
       <c r="E100" s="3">
-        <v>-1597900</v>
+        <v>-1778300</v>
       </c>
       <c r="F100" s="3">
-        <v>-892700</v>
+        <v>-993500</v>
       </c>
       <c r="G100" s="3">
-        <v>-2975400</v>
+        <v>-3311200</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3213,16 +3213,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>210000</v>
+        <v>233700</v>
       </c>
       <c r="E101" s="3">
-        <v>172000</v>
+        <v>191400</v>
       </c>
       <c r="F101" s="3">
-        <v>259500</v>
+        <v>288700</v>
       </c>
       <c r="G101" s="3">
-        <v>52000</v>
+        <v>57900</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3243,16 +3243,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>70100</v>
+        <v>78100</v>
       </c>
       <c r="E102" s="3">
-        <v>-491000</v>
+        <v>-546500</v>
       </c>
       <c r="F102" s="3">
-        <v>860100</v>
+        <v>957200</v>
       </c>
       <c r="G102" s="3">
-        <v>-710500</v>
+        <v>-790600</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>SSUMY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,14 +693,14 @@
       <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>43921</v>
+      </c>
+      <c r="I7" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43190</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -712,25 +712,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>49063100</v>
+        <v>45686400</v>
       </c>
       <c r="E8" s="3">
-        <v>48406900</v>
+        <v>51287600</v>
       </c>
       <c r="F8" s="3">
-        <v>39014600</v>
+        <v>45251000</v>
       </c>
       <c r="G8" s="3">
-        <v>32979900</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>41999100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>49253900</v>
+      </c>
+      <c r="I8" s="3">
+        <v>48183700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>45452900</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -742,25 +742,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>39531500</v>
+        <v>36810800</v>
       </c>
       <c r="E9" s="3">
-        <v>39640200</v>
+        <v>41999200</v>
       </c>
       <c r="F9" s="3">
-        <v>31846400</v>
+        <v>36937000</v>
       </c>
       <c r="G9" s="3">
-        <v>27800700</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>35403600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>41134500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>39852400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>36447000</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -772,25 +772,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>9531700</v>
+        <v>8875700</v>
       </c>
       <c r="E10" s="3">
-        <v>8766700</v>
+        <v>9288500</v>
       </c>
       <c r="F10" s="3">
-        <v>7168200</v>
+        <v>8314000</v>
       </c>
       <c r="G10" s="3">
-        <v>5179200</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>6595500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>8119400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>8331300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>9005900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -876,25 +876,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>265600</v>
+        <v>178200</v>
       </c>
       <c r="E14" s="3">
-        <v>48700</v>
+        <v>-318500</v>
       </c>
       <c r="F14" s="3">
-        <v>127000</v>
+        <v>-563100</v>
       </c>
       <c r="G14" s="3">
-        <v>574900</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>748100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>381700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-220300</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -906,25 +906,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>156600</v>
+        <v>145800</v>
       </c>
       <c r="E15" s="3">
-        <v>125700</v>
+        <v>133100</v>
       </c>
       <c r="F15" s="3">
-        <v>122700</v>
+        <v>142400</v>
       </c>
       <c r="G15" s="3">
-        <v>137400</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>175000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1536600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>163000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>180300</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -947,25 +947,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>46548300</v>
+        <v>42943400</v>
       </c>
       <c r="E17" s="3">
-        <v>45332100</v>
+        <v>48105500</v>
       </c>
       <c r="F17" s="3">
-        <v>36608400</v>
+        <v>42816300</v>
       </c>
       <c r="G17" s="3">
-        <v>33398000</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>41542300</v>
+      </c>
+      <c r="H17" s="3">
+        <v>47430200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>45700500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>43335700</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -977,25 +977,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2514800</v>
+        <v>2743000</v>
       </c>
       <c r="E18" s="3">
-        <v>3074800</v>
+        <v>3182100</v>
       </c>
       <c r="F18" s="3">
-        <v>2406200</v>
+        <v>2434800</v>
       </c>
       <c r="G18" s="3">
-        <v>-418100</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>456800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1823700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2483200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2117200</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1021,25 +1021,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1858600</v>
+        <v>-941100</v>
       </c>
       <c r="E20" s="3">
-        <v>2483900</v>
+        <v>-1874200</v>
       </c>
       <c r="F20" s="3">
-        <v>1997300</v>
+        <v>-1646400</v>
       </c>
       <c r="G20" s="3">
-        <v>-33000</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>588900</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-940800</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1169700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1498500</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5784600</v>
+        <v>3829900</v>
       </c>
       <c r="E21" s="3">
-        <v>6854100</v>
+        <v>5189500</v>
       </c>
       <c r="F21" s="3">
-        <v>5604600</v>
+        <v>4223600</v>
       </c>
       <c r="G21" s="3">
-        <v>753800</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>43000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>4301000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3815900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3796100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1081,25 +1081,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>627100</v>
+        <v>584000</v>
       </c>
       <c r="E22" s="3">
-        <v>424500</v>
+        <v>449800</v>
       </c>
       <c r="F22" s="3">
-        <v>214400</v>
+        <v>248600</v>
       </c>
       <c r="G22" s="3">
-        <v>217800</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>277400</v>
+      </c>
+      <c r="H22" s="3">
+        <v>429300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>365800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>313500</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1111,25 +1111,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3746300</v>
+        <v>3488500</v>
       </c>
       <c r="E23" s="3">
-        <v>5134200</v>
+        <v>5439700</v>
       </c>
       <c r="F23" s="3">
-        <v>4189100</v>
+        <v>4858800</v>
       </c>
       <c r="G23" s="3">
-        <v>-668900</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>-851900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2341200</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3646000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3882100</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>720900</v>
+        <v>671300</v>
       </c>
       <c r="E24" s="3">
-        <v>879500</v>
+        <v>931900</v>
       </c>
       <c r="F24" s="3">
-        <v>748700</v>
+        <v>868400</v>
       </c>
       <c r="G24" s="3">
-        <v>285900</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>364100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>580000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>597700</v>
+      </c>
+      <c r="J24" s="3">
+        <v>738100</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1201,25 +1201,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3025400</v>
+        <v>2817200</v>
       </c>
       <c r="E26" s="3">
-        <v>4254700</v>
+        <v>4507900</v>
       </c>
       <c r="F26" s="3">
-        <v>3440400</v>
+        <v>3990400</v>
       </c>
       <c r="G26" s="3">
-        <v>-954800</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>-1216000</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1761300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>3048300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3144000</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1231,25 +1231,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2741600</v>
+        <v>2552900</v>
       </c>
       <c r="E27" s="3">
-        <v>4012000</v>
+        <v>4250800</v>
       </c>
       <c r="F27" s="3">
-        <v>3290700</v>
+        <v>3816700</v>
       </c>
       <c r="G27" s="3">
-        <v>-1086400</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>-1383500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1592500</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2892300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2905000</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1381,25 +1381,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1858600</v>
+        <v>941100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2483900</v>
+        <v>1874200</v>
       </c>
       <c r="F32" s="3">
-        <v>-1997300</v>
+        <v>1646400</v>
       </c>
       <c r="G32" s="3">
-        <v>33000</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-588900</v>
+      </c>
+      <c r="H32" s="3">
+        <v>940800</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1169700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1498500</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1411,25 +1411,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2741600</v>
+        <v>2554300</v>
       </c>
       <c r="E33" s="3">
-        <v>4012000</v>
+        <v>4252700</v>
       </c>
       <c r="F33" s="3">
-        <v>3290700</v>
+        <v>3818500</v>
       </c>
       <c r="G33" s="3">
-        <v>-1086400</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>-1384000</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1592500</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2892500</v>
+      </c>
+      <c r="J33" s="3">
+        <v>2905000</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1471,25 +1471,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2741600</v>
+        <v>2554300</v>
       </c>
       <c r="E35" s="3">
-        <v>4012000</v>
+        <v>4252700</v>
       </c>
       <c r="F35" s="3">
-        <v>3290700</v>
+        <v>3818500</v>
       </c>
       <c r="G35" s="3">
-        <v>-1086400</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>-1384000</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1592500</v>
+      </c>
+      <c r="I35" s="3">
+        <v>2892500</v>
+      </c>
+      <c r="J35" s="3">
+        <v>2905000</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1517,14 +1517,14 @@
       <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="H38" s="2">
+        <v>43921</v>
+      </c>
+      <c r="I38" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43190</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1564,25 +1564,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4815900</v>
+        <v>4415400</v>
       </c>
       <c r="E41" s="3">
-        <v>4740300</v>
+        <v>4941200</v>
       </c>
       <c r="F41" s="3">
-        <v>5308500</v>
+        <v>6043000</v>
       </c>
       <c r="G41" s="3">
-        <v>4343500</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>5416100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>6601800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>5959400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>6281700</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1594,25 +1594,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1347800</v>
+        <v>154300</v>
       </c>
       <c r="E42" s="3">
-        <v>891500</v>
+        <v>94200</v>
       </c>
       <c r="F42" s="3">
-        <v>1797700</v>
+        <v>133000</v>
       </c>
       <c r="G42" s="3">
-        <v>828300</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>129900</v>
+      </c>
+      <c r="H42" s="3">
+        <v>114100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>112600</v>
+      </c>
+      <c r="J42" s="3">
+        <v>155800</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1624,25 +1624,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16221500</v>
+        <v>15285700</v>
       </c>
       <c r="E43" s="3">
-        <v>14948100</v>
+        <v>16027000</v>
       </c>
       <c r="F43" s="3">
-        <v>13649000</v>
+        <v>16024100</v>
       </c>
       <c r="G43" s="3">
-        <v>10596300</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>13815400</v>
+      </c>
+      <c r="H43" s="3">
+        <v>12530600</v>
+      </c>
+      <c r="I43" s="3">
+        <v>12838100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>12696800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1654,25 +1654,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10556100</v>
+        <v>9829600</v>
       </c>
       <c r="E44" s="3">
-        <v>19745900</v>
+        <v>10460500</v>
       </c>
       <c r="F44" s="3">
-        <v>7511800</v>
+        <v>8712600</v>
       </c>
       <c r="G44" s="3">
-        <v>5632300</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>7172600</v>
+      </c>
+      <c r="H44" s="3">
+        <v>8642800</v>
+      </c>
+      <c r="I44" s="3">
+        <v>8349500</v>
+      </c>
+      <c r="J44" s="3">
+        <v>8265200</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1684,25 +1684,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4232200</v>
+        <v>4930100</v>
       </c>
       <c r="E45" s="3">
-        <v>4145200</v>
+        <v>5134000</v>
       </c>
       <c r="F45" s="3">
-        <v>4715900</v>
+        <v>7342500</v>
       </c>
       <c r="G45" s="3">
-        <v>3432500</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>5090100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>4976200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4756000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>5341700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1714,25 +1714,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>37173500</v>
+        <v>34615100</v>
       </c>
       <c r="E46" s="3">
-        <v>34598000</v>
+        <v>36657000</v>
       </c>
       <c r="F46" s="3">
-        <v>32982900</v>
+        <v>38255200</v>
       </c>
       <c r="G46" s="3">
-        <v>24832800</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>31624000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>32865500</v>
+      </c>
+      <c r="I46" s="3">
+        <v>32015600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>32741300</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1744,25 +1744,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>26789500</v>
+        <v>22104700</v>
       </c>
       <c r="E47" s="3">
-        <v>24341800</v>
+        <v>22796900</v>
       </c>
       <c r="F47" s="3">
-        <v>22677400</v>
+        <v>22840800</v>
       </c>
       <c r="G47" s="3">
-        <v>20205500</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>22776600</v>
+      </c>
+      <c r="H47" s="3">
+        <v>22157700</v>
+      </c>
+      <c r="I47" s="3">
+        <v>23103100</v>
+      </c>
+      <c r="J47" s="3">
+        <v>23136500</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1774,25 +1774,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11269100</v>
+        <v>7586100</v>
       </c>
       <c r="E48" s="3">
-        <v>20037900</v>
+        <v>7841200</v>
       </c>
       <c r="F48" s="3">
-        <v>9963500</v>
+        <v>8390100</v>
       </c>
       <c r="G48" s="3">
-        <v>10062700</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>9359000</v>
+      </c>
+      <c r="H48" s="3">
+        <v>9795700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>6738100</v>
+      </c>
+      <c r="J48" s="3">
+        <v>7063900</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1804,25 +1804,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2483800</v>
+        <v>2343200</v>
       </c>
       <c r="E49" s="3">
-        <v>4044000</v>
+        <v>2172100</v>
       </c>
       <c r="F49" s="3">
-        <v>1810300</v>
+        <v>2139900</v>
       </c>
       <c r="G49" s="3">
-        <v>1817300</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>2454900</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2685000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2344200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2490200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1894,25 +1894,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>615500</v>
+        <v>4649000</v>
       </c>
       <c r="E52" s="3">
-        <v>636500</v>
+        <v>4761200</v>
       </c>
       <c r="F52" s="3">
-        <v>599200</v>
+        <v>5284600</v>
       </c>
       <c r="G52" s="3">
-        <v>449500</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>4462500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4601100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3562400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3748500</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -1954,25 +1954,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>78331300</v>
+        <v>72940300</v>
       </c>
       <c r="E54" s="3">
-        <v>71748200</v>
+        <v>76018000</v>
       </c>
       <c r="F54" s="3">
-        <v>68033400</v>
+        <v>78908400</v>
       </c>
       <c r="G54" s="3">
-        <v>57367900</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>73056600</v>
+      </c>
+      <c r="H54" s="3">
+        <v>75543200</v>
+      </c>
+      <c r="I54" s="3">
+        <v>71442300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>73166300</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2012,25 +2012,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12168900</v>
+        <v>11331400</v>
       </c>
       <c r="E57" s="3">
-        <v>11707700</v>
+        <v>12404500</v>
       </c>
       <c r="F57" s="3">
-        <v>11448600</v>
+        <v>13278700</v>
       </c>
       <c r="G57" s="3">
-        <v>9014400</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>11479600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>10028600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>10177600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>9598000</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2042,25 +2042,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5842100</v>
+        <v>5440100</v>
       </c>
       <c r="E58" s="3">
-        <v>10272100</v>
+        <v>5727800</v>
       </c>
       <c r="F58" s="3">
-        <v>4841100</v>
+        <v>5615000</v>
       </c>
       <c r="G58" s="3">
-        <v>3898400</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>4964500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>7625900</v>
+      </c>
+      <c r="I58" s="3">
+        <v>6263600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5861800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2072,25 +2072,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4287100</v>
+        <v>3017600</v>
       </c>
       <c r="E59" s="3">
-        <v>3938800</v>
+        <v>3141200</v>
       </c>
       <c r="F59" s="3">
-        <v>5555500</v>
+        <v>5455500</v>
       </c>
       <c r="G59" s="3">
-        <v>3192900</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>3198800</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2802600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3274500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4015500</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2102,25 +2102,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>22298100</v>
+        <v>20763500</v>
       </c>
       <c r="E60" s="3">
-        <v>21052600</v>
+        <v>22305500</v>
       </c>
       <c r="F60" s="3">
-        <v>21845200</v>
+        <v>25337100</v>
       </c>
       <c r="G60" s="3">
-        <v>16105700</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>20510200</v>
+      </c>
+      <c r="H60" s="3">
+        <v>21343000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>20564100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>20320600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2132,25 +2132,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20476400</v>
+        <v>19067200</v>
       </c>
       <c r="E61" s="3">
-        <v>20508300</v>
+        <v>21728800</v>
       </c>
       <c r="F61" s="3">
-        <v>20045900</v>
+        <v>23250200</v>
       </c>
       <c r="G61" s="3">
-        <v>20338200</v>
+        <v>25900300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>26586600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>22310600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>24979400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2162,25 +2162,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2383400</v>
+        <v>1017400</v>
       </c>
       <c r="E62" s="3">
-        <v>1953500</v>
+        <v>1164600</v>
       </c>
       <c r="F62" s="3">
-        <v>2135100</v>
+        <v>1666600</v>
       </c>
       <c r="G62" s="3">
-        <v>1785500</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>1290800</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1389300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1153300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1187700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2282,25 +2282,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>46768300</v>
+        <v>42050000</v>
       </c>
       <c r="E66" s="3">
-        <v>44919500</v>
+        <v>46104000</v>
       </c>
       <c r="F66" s="3">
-        <v>45328900</v>
+        <v>51063800</v>
       </c>
       <c r="G66" s="3">
-        <v>39419400</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>48684300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>50519600</v>
+      </c>
+      <c r="I66" s="3">
+        <v>45215400</v>
+      </c>
+      <c r="J66" s="3">
+        <v>47797300</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2446,25 +2446,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>20576200</v>
+        <v>19160100</v>
       </c>
       <c r="E72" s="3">
-        <v>19216600</v>
+        <v>20360200</v>
       </c>
       <c r="F72" s="3">
-        <v>16114600</v>
+        <v>18690500</v>
       </c>
       <c r="G72" s="3">
-        <v>13287000</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>16920700</v>
+      </c>
+      <c r="H72" s="3">
+        <v>19273700</v>
+      </c>
+      <c r="I72" s="3">
+        <v>18602200</v>
+      </c>
+      <c r="J72" s="3">
+        <v>17211900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2566,25 +2566,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>31563000</v>
+        <v>29390700</v>
       </c>
       <c r="E76" s="3">
-        <v>26828700</v>
+        <v>28425300</v>
       </c>
       <c r="F76" s="3">
-        <v>22704500</v>
+        <v>26333800</v>
       </c>
       <c r="G76" s="3">
-        <v>17948500</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>22856900</v>
+      </c>
+      <c r="H76" s="3">
+        <v>23643900</v>
+      </c>
+      <c r="I76" s="3">
+        <v>25011100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>24087000</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2642,14 +2642,14 @@
       <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="H80" s="2">
+        <v>43921</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43555</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43190</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2661,25 +2661,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2741600</v>
+        <v>2554300</v>
       </c>
       <c r="E81" s="3">
-        <v>4012000</v>
+        <v>4252700</v>
       </c>
       <c r="F81" s="3">
-        <v>3290700</v>
+        <v>3818500</v>
       </c>
       <c r="G81" s="3">
-        <v>-1086400</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>-1384000</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1592500</v>
+      </c>
+      <c r="I81" s="3">
+        <v>2892500</v>
+      </c>
+      <c r="J81" s="3">
+        <v>2905000</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2705,25 +2705,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1421200</v>
+        <v>1176800</v>
       </c>
       <c r="E83" s="3">
-        <v>1304600</v>
+        <v>1247900</v>
       </c>
       <c r="F83" s="3">
-        <v>1209600</v>
+        <v>1259000</v>
       </c>
       <c r="G83" s="3">
-        <v>1213400</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>1370400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1536600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>791200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>871600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -2885,25 +2885,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4350600</v>
+        <v>4025300</v>
       </c>
       <c r="E89" s="3">
-        <v>1690200</v>
+        <v>1751300</v>
       </c>
       <c r="F89" s="3">
-        <v>1313700</v>
+        <v>1598100</v>
       </c>
       <c r="G89" s="3">
-        <v>3315500</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>4223300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>3035400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>2426500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>2780100</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2929,25 +2929,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-663000</v>
+        <v>-617400</v>
       </c>
       <c r="E91" s="3">
-        <v>-499100</v>
+        <v>-528800</v>
       </c>
       <c r="F91" s="3">
-        <v>-495000</v>
+        <v>-574100</v>
       </c>
       <c r="G91" s="3">
-        <v>-471000</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-599800</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-715000</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-992900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-920500</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3019,25 +3019,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1556400</v>
+        <v>-1449300</v>
       </c>
       <c r="E94" s="3">
-        <v>-649800</v>
+        <v>-688500</v>
       </c>
       <c r="F94" s="3">
-        <v>348200</v>
+        <v>403800</v>
       </c>
       <c r="G94" s="3">
-        <v>-852800</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-1086000</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-1890500</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-463100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1466700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3063,25 +3063,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1046000</v>
+        <v>974000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1087300</v>
+        <v>1152000</v>
       </c>
       <c r="F96" s="3">
-        <v>-709900</v>
+        <v>823400</v>
       </c>
       <c r="G96" s="3">
-        <v>-621000</v>
+        <v>790800</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>847400</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>622900</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2949900</v>
+        <v>-2746900</v>
       </c>
       <c r="E100" s="3">
-        <v>-1778300</v>
+        <v>-1884100</v>
       </c>
       <c r="F100" s="3">
-        <v>-993500</v>
+        <v>-1152300</v>
       </c>
       <c r="G100" s="3">
-        <v>-3311200</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-4216700</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-536600</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-2104500</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-2162000</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3213,25 +3213,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>233700</v>
+        <v>217700</v>
       </c>
       <c r="E101" s="3">
-        <v>191400</v>
+        <v>202800</v>
       </c>
       <c r="F101" s="3">
-        <v>288700</v>
+        <v>334900</v>
       </c>
       <c r="G101" s="3">
-        <v>57900</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>73700</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-148200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>43500</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-138300</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3243,25 +3243,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>78100</v>
+        <v>46800</v>
       </c>
       <c r="E102" s="3">
-        <v>-546500</v>
+        <v>-618500</v>
       </c>
       <c r="F102" s="3">
-        <v>957200</v>
+        <v>1184600</v>
       </c>
       <c r="G102" s="3">
-        <v>-790600</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-1005700</v>
+      </c>
+      <c r="H102" s="3">
+        <v>460200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-97500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-986800</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>SSUMY</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>48695700</v>
+      </c>
+      <c r="E8" s="3">
         <v>45686400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>51287600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45251000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41999100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49253900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>48183700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45452900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>39047800</v>
+      </c>
+      <c r="E9" s="3">
         <v>36810800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>41999200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>36937000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35403600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>41134500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39852400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36447000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9647900</v>
+      </c>
+      <c r="E10" s="3">
         <v>8875700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9288500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8314000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6595500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8119400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8331300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9005900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-252600</v>
+      </c>
+      <c r="E14" s="3">
         <v>178200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-318500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-563100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>748100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>381700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-220300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1465600</v>
+      </c>
+      <c r="E15" s="3">
         <v>145800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>133100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>142400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>175000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1536600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>163000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>180300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45991000</v>
+      </c>
+      <c r="E17" s="3">
         <v>42943400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48105500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42816300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41542300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47430200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45700500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43335700</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2704700</v>
+      </c>
+      <c r="E18" s="3">
         <v>2743000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3182100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2434800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>456800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1823700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2483200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2117200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,158 +1047,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1769900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-941100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1874200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1646400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>588900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-940800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1169700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1498500</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5940200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3829900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5189500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4223600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>43000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4301000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3815900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3796100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>654100</v>
+      </c>
+      <c r="E22" s="3">
         <v>584000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>449800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>248600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>277400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>429300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>365800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>313500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4644900</v>
+      </c>
+      <c r="E23" s="3">
         <v>3488500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5439700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4858800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-851900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2341200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3646000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3882100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>578300</v>
+      </c>
+      <c r="E24" s="3">
         <v>671300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>931900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>868400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>364100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>580000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>597700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>738100</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4066600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2817200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4507900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3990400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1216000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1761300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3048300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3144000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3749700</v>
+      </c>
+      <c r="E27" s="3">
         <v>2552900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4250800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3816700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1383500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1592500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2892300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2905000</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1769900</v>
+      </c>
+      <c r="E32" s="3">
         <v>941100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1874200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1646400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-588900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>940800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1169700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1498500</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3752000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2554300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4252700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3818500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1384000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1592500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2892500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2905000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3752000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2554300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4252700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3818500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1384000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1592500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2892500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2905000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,278 +1643,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3810500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4415400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4941200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6043000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5416100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6601800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5959400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6281700</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>128800</v>
+      </c>
+      <c r="E42" s="3">
         <v>154300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>94200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>133000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>129900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>114100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>112600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>155800</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13701300</v>
+      </c>
+      <c r="E43" s="3">
         <v>15285700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16027000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16024100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13815400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12530600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12838100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12696800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11044200</v>
+      </c>
+      <c r="E44" s="3">
         <v>9829600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10460500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8712600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7172600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8642800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8349500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8265200</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5199700</v>
+      </c>
+      <c r="E45" s="3">
         <v>4930100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5134000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7342500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5090100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4976200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4756000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5341700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33884500</v>
+      </c>
+      <c r="E46" s="3">
         <v>34615100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36657000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38255200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>31624000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32865500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>32015600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>32741300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>23026200</v>
+      </c>
+      <c r="E47" s="3">
         <v>22104700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>22796900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>22840800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>22776600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>22157700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>23103100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>23136500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8231200</v>
+      </c>
+      <c r="E48" s="3">
         <v>7586100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7841200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8390100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9359000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9795700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6738100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7063900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4278700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2343200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2172100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2139900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2454900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2685000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2344200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2490200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4639900</v>
+      </c>
+      <c r="E52" s="3">
         <v>4649000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4761200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5284600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4462500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4601100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3562400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3748500</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>77671600</v>
+      </c>
+      <c r="E54" s="3">
         <v>72940300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76018000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78908400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73056600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75543200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71442300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>73166300</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12168700</v>
+      </c>
+      <c r="E57" s="3">
         <v>11331400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12404500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13278700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11479600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10028600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10177600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9598000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4467100</v>
+      </c>
+      <c r="E58" s="3">
         <v>5440100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5727800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5615000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4964500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7625900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6263600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5861800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4148000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3017600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3141200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5455500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3198800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2802600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3274500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4015500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21780900</v>
+      </c>
+      <c r="E60" s="3">
         <v>20763500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22305500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25337100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20510200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21343000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20564100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20320600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20799600</v>
+      </c>
+      <c r="E61" s="3">
         <v>19067200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21728800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23250200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25900300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26586600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22310600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24979400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1249800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1017400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1164600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1666600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1290800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1389300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1153300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1187700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45046400</v>
+      </c>
+      <c r="E66" s="3">
         <v>42050000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>46104000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>51063800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48684300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50519600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45215400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47797300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22021600</v>
+      </c>
+      <c r="E72" s="3">
         <v>19160100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20360200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18690500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16920700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19273700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18602200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17211900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31041900</v>
+      </c>
+      <c r="E76" s="3">
         <v>29390700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28425300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26333800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22856900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23643900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25011100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24087000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3752000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2554300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4252700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3818500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1384000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1592500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2892500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2905000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1465600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1176800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1247900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1259000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1370400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1536600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>791200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>871600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4088700</v>
+      </c>
+      <c r="E89" s="3">
         <v>4025300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1751300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1598100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4223300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3035400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2426500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2780100</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-686500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-617400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-528800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-574100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-599800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-715000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-992900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-920500</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3081100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1449300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-688500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>403800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1086000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1890500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-463100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1466700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1035200</v>
+      </c>
+      <c r="E96" s="3">
         <v>974000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1152000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>823400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>790800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>847400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>800000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>622900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1652000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2746900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1884100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1152300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4216700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-536600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2104500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2162000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>217700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>202800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>334900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>73700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-148200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>43500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-138300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-649300</v>
+      </c>
+      <c r="E102" s="3">
         <v>46800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-618500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1184600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1005700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>460200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-97500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-986800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSUMY_YR_FIN.xlsx
@@ -928,7 +928,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1465600</v>
+        <v>176200</v>
       </c>
       <c r="E15" s="3">
         <v>145800</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5940200</v>
+        <v>4650700</v>
       </c>
       <c r="E21" s="3">
         <v>3829900</v>
@@ -1716,10 +1716,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13701300</v>
+        <v>13774600</v>
       </c>
       <c r="E43" s="3">
-        <v>15285700</v>
+        <v>13317100</v>
       </c>
       <c r="F43" s="3">
         <v>16027000</v>
@@ -1782,7 +1782,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5199700</v>
+        <v>5126400</v>
       </c>
       <c r="E45" s="3">
         <v>4930100</v>
@@ -1818,7 +1818,7 @@
         <v>33884500</v>
       </c>
       <c r="E46" s="3">
-        <v>34615100</v>
+        <v>32646400</v>
       </c>
       <c r="F46" s="3">
         <v>36657000</v>
@@ -1881,7 +1881,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8231200</v>
+        <v>8161900</v>
       </c>
       <c r="E48" s="3">
         <v>7586100</v>
@@ -1914,7 +1914,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4278700</v>
+        <v>4348000</v>
       </c>
       <c r="E49" s="3">
         <v>2343200</v>
@@ -2903,7 +2903,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1465600</v>
+        <v>1289400</v>
       </c>
       <c r="E83" s="3">
         <v>1176800</v>
